--- a/inventario-de-anexos.xlsx
+++ b/inventario-de-anexos.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="210">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -568,6 +568,93 @@
   </si>
   <si>
     <t xml:space="preserve">   e nas capas dos PDFs. Causa recorrente de ressalva em prestação de contas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18b7bbb11b6157af525c7e1c88b7e385763dadc094bb60fdf6f3a27d9c2aff91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonte canônica local: relatorios/relatorio-tecnico-recanto-da-serra.pdf, 14 páginas, título interno 'RELATÓRIO TÉCNICO – RECANTO DA SERRA'. SHA-256 é do original local, NÃO de objeto espelhado: nada foi enviado a storage. Contém a seção que serve de fonte a A05. Exige revisão de privacidade — nomeia trabalhadores remunerados. Não promovido a PUBLICAVEL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6dfef47006ed97133c8fef2ce0b935643c7955efbc7abaece2bcc9b0edcfea2e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonte canônica local: relatorios/relatorio-tecnico-borda-da-mata.pdf, 7 páginas, título interno 'RELATÓRIO TÉCNICO – BORDA DA MATA'. PDF sem camada de texto: 7 imagens JPEG, zero fontes. Derivado existente: derivados/a03-borda-da-mata-ocr.md, sha256 502d9bf1433413cfd17fe70442f6351efbe708aad7a94314946b2b64b366ff8b, produzido por TRANSCRIÇÃO ASSISTIDA POR LEITURA VISUAL — não por OCR estatístico. Original preservado e RESTRITO até revisão. O valor em 'Link atual' é compartilhado com A02 e A04 e não identifica este item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7e966429d1fccae8f7583ebc0fb6644c8f6393390e5a2a0d633cbe79a79a7cde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonte canônica local: relatorios/relatorio-tecnico-serra-dos-macacos.pdf, 4 páginas. Título interno é 'RELATO TÉCNICO SERRA DOS MACACOS' — 'RELATO', não 'RELATÓRIO'. Divergência registrada, não corrigida. O valor em 'Link atual' é compartilhado com A02 e A03 e não identifica este item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">derivavel_de = A02. Seção comprovada no original de A02: 'Diagnóstico detalhado do Recanto da Serra'. O artefato A05 separado ainda NÃO existe, por isso o status permanece Pendente e não ESPELHAVEL. Não extraído nesta rodada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">derivavel_de = A03. Seção comprovada na transcrição derivada de A03: 'Resumo Executivo: Diagnóstico de Impacto Econômico e Cultural – Borda da Mata', mais o detalhamento numerado. O artefato A06 separado ainda NÃO existe, por isso o status permanece Pendente e não ESPELHAVEL. Não extraído nesta rodada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrevista — Maria Madalena Santos (Dona Madá), Ilha Grande</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconciliado em 2026-09-06. Nome declarado: Maria Madalena Santos; nome de exibição: Dona Madá. Descrição sustentada: moradora / memória local. RETIRADOS por falta de fonte, e registrados aqui como proveniência: a data '11/04/2026' e a classificação 'liderança', ambas presentes antes e não confirmadas por nenhum arquivo do acervo. Consentimento: verbal_gravado; declaracao_responsavel = autorizado; evidencia_transcricao = nao_localizada; evidencia_audio = pendente_verificacao. Fonte canônica local: entrevistas/08-dona-mada/. Não promovido a PUBLICAVEL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERMANECE como previsão de entrevista de Itabaianinha que NÃO se realizou. Não foi reclassificado como Tomar do Geru e não recebeu arquivo. B13 não o substitui: é item complementar de outra entrevista, de outro município. Continua no conjunto dos 28 itens obrigatórios, como pendência real.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instrumento_original_separado = nao_localizado. fonte_das_perguntas = cabecalhos_das_planilhas. Reconstituível a partir de formularios/formulario-de-funcionamento-pedro-e-oviedo.xlsx, cujos cabeçalhos são o texto das perguntas aplicadas. Qualquer documento gerado assim é 'Reconstituição do instrumento de coleta', não o instrumento original. Respostas individuais são RESTRITO — a planilha tem coluna com nome de responsável. PDF não produzido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instrumento_original_separado = nao_localizado. fonte_das_perguntas = cabecalhos_das_planilhas. Reconstituível a partir de formularios/formulario-recanto-da-serra-respostas.xlsx e formularios/formulario-borda-da-mata-respostas.xlsx. Qualquer documento gerado assim é 'Reconstituição do instrumento de coleta'. Respostas individuais são RESTRITO. PDF não produzido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrevista — Laerte Santos Aguiar, Secretário Municipal de Cultura de Tomar do Geru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entrevista-laerte-aguiar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVIDÊNCIA COMPLEMENTAR — não exigida pelo edital; obrigatorio = false. Estado preliminar: RESTRITO. NÃO substitui B07, que segue como previsão não realizada de Itabaianinha. Nome declarado: Laerte Santos Aguiar. Função: Secretário Municipal de Cultura. Município: Tomar do Geru. Fonte canônica local: entrevistas/07-laerte-aguiar/ — áudio e transcrição. Consentimento verbal gravado, evidência localizada na transcrição. Participante adicional sustentado pela fonte: Mateus Cardoso Rita, sacristão, que também autoriza a gravação e não é entrevistado principal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrevista — Márcio André, Diretor de Turismo de São Cristóvão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entrevista-marcio-andre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVIDÊNCIA COMPLEMENTAR — não exigida pelo edital; obrigatorio = false. Estado preliminar: RESTRITO. Nome declarado: Márcio André Soares Ramos; nome de exibição: Márcio André. Função: Diretor de Turismo de São Cristóvão. Fonte canônica local: entrevistas/04-diretor-turismo-sao-cristovao/. Consentimento verbal gravado, evidência localizada na transcrição. Participante adicional sustentado pela fonte: Ian Victor Batista de Araújo, que também autoriza a gravação; NÃO é segundo entrevistado principal. A grafia 'marcio-ramos', presente em nome de foto, é nomenclatura histórica divergente do mesmo nome, não outra pessoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anexo Técnico de Indicadores — Etapa 1 de Levantamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anexo-indicadores-etapa-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVIDÊNCIA COMPLEMENTAR — não exigida pelo edital; obrigatorio = false. Não foi exigido pela FUNCAP. Estado preliminar: RESTRITO, porque o conjunto contém arquivos que exigem revisão de privacidade — 06-pessoas-trabalho e 08-fornecedores nomeiam pessoas. NÃO substitui A01, que continua representando o painel interativo no Figma. Fonte canônica local: formularios/indicadores-observatorio/ — uma planilha de 17 abas mais 17 PDFs que a renderizam, aba por aba. A nota metodológica desse conjunto é a origem da regra de anonimização de comentários que citam terceiros.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natureza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item_exigido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item_nao_exigido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evidencia_complementar</t>
   </si>
 </sst>
 </file>
@@ -1101,7 +1188,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -1166,6 +1253,9 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -1201,6 +1291,9 @@
       <c r="M2" s="6"/>
       <c r="N2" s="7"/>
       <c r="O2" s="6"/>
+      <c r="P2" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
@@ -1234,8 +1327,15 @@
       <c r="K3" s="5"/>
       <c r="L3" s="4"/>
       <c r="M3" s="6"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="6"/>
+      <c r="N3" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -1269,8 +1369,15 @@
       <c r="K4" s="5"/>
       <c r="L4" s="4"/>
       <c r="M4" s="6"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="6"/>
+      <c r="N4" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -1304,8 +1411,15 @@
       <c r="K5" s="5"/>
       <c r="L5" s="4"/>
       <c r="M5" s="6"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="6"/>
+      <c r="N5" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -1336,7 +1450,12 @@
       <c r="L6" s="4"/>
       <c r="M6" s="6"/>
       <c r="N6" s="7"/>
-      <c r="O6" s="6"/>
+      <c r="O6" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -1367,7 +1486,12 @@
       <c r="L7" s="4"/>
       <c r="M7" s="6"/>
       <c r="N7" s="7"/>
-      <c r="O7" s="6"/>
+      <c r="O7" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
@@ -1399,6 +1523,9 @@
       <c r="M8" s="6"/>
       <c r="N8" s="7"/>
       <c r="O8" s="6"/>
+      <c r="P8" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
@@ -1430,6 +1557,9 @@
       <c r="M9" s="6"/>
       <c r="N9" s="7"/>
       <c r="O9" s="6"/>
+      <c r="P9" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
@@ -1464,7 +1594,12 @@
       <c r="L10" s="4"/>
       <c r="M10" s="6"/>
       <c r="N10" s="7"/>
-      <c r="O10" s="6"/>
+      <c r="O10" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
@@ -1499,7 +1634,12 @@
       <c r="L11" s="4"/>
       <c r="M11" s="6"/>
       <c r="N11" s="7"/>
-      <c r="O11" s="6"/>
+      <c r="O11" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
@@ -1535,6 +1675,9 @@
       <c r="M12" s="6"/>
       <c r="N12" s="7"/>
       <c r="O12" s="6"/>
+      <c r="P12" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
@@ -1570,6 +1713,9 @@
       <c r="M13" s="6"/>
       <c r="N13" s="7"/>
       <c r="O13" s="6"/>
+      <c r="P13" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
@@ -1605,6 +1751,9 @@
       <c r="M14" s="6"/>
       <c r="N14" s="7"/>
       <c r="O14" s="6"/>
+      <c r="P14" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
@@ -1640,6 +1789,9 @@
       <c r="M15" s="6"/>
       <c r="N15" s="7"/>
       <c r="O15" s="6"/>
+      <c r="P15" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
@@ -1675,6 +1827,9 @@
       <c r="M16" s="6"/>
       <c r="N16" s="7"/>
       <c r="O16" s="6"/>
+      <c r="P16" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
@@ -1684,7 +1839,7 @@
         <v>61</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>69</v>
@@ -1709,7 +1864,12 @@
       <c r="L17" s="4"/>
       <c r="M17" s="6"/>
       <c r="N17" s="7"/>
-      <c r="O17" s="6"/>
+      <c r="O17" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
@@ -1740,7 +1900,12 @@
       <c r="L18" s="4"/>
       <c r="M18" s="6"/>
       <c r="N18" s="7"/>
-      <c r="O18" s="6"/>
+      <c r="O18" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
@@ -1772,6 +1937,9 @@
       <c r="M19" s="6"/>
       <c r="N19" s="7"/>
       <c r="O19" s="6"/>
+      <c r="P19" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
@@ -1803,6 +1971,9 @@
       <c r="M20" s="6"/>
       <c r="N20" s="7"/>
       <c r="O20" s="6"/>
+      <c r="P20" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
@@ -1834,6 +2005,9 @@
       <c r="M21" s="6"/>
       <c r="N21" s="7"/>
       <c r="O21" s="6"/>
+      <c r="P21" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
@@ -1865,6 +2039,9 @@
       <c r="M22" s="6"/>
       <c r="N22" s="7"/>
       <c r="O22" s="6"/>
+      <c r="P22" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
@@ -1896,6 +2073,9 @@
       <c r="M23" s="6"/>
       <c r="N23" s="7"/>
       <c r="O23" s="6"/>
+      <c r="P23" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
@@ -1929,6 +2109,9 @@
       <c r="M24" s="6"/>
       <c r="N24" s="7"/>
       <c r="O24" s="6"/>
+      <c r="P24" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
@@ -1960,6 +2143,9 @@
       <c r="M25" s="6"/>
       <c r="N25" s="7"/>
       <c r="O25" s="6"/>
+      <c r="P25" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
@@ -1991,6 +2177,9 @@
       <c r="M26" s="6"/>
       <c r="N26" s="7"/>
       <c r="O26" s="6"/>
+      <c r="P26" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
@@ -2022,6 +2211,9 @@
       <c r="M27" s="6"/>
       <c r="N27" s="7"/>
       <c r="O27" s="6"/>
+      <c r="P27" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
@@ -2057,6 +2249,9 @@
       <c r="M28" s="6"/>
       <c r="N28" s="7"/>
       <c r="O28" s="6"/>
+      <c r="P28" s="6" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
@@ -2092,6 +2287,9 @@
       <c r="M29" s="6"/>
       <c r="N29" s="7"/>
       <c r="O29" s="6"/>
+      <c r="P29" s="6" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
@@ -2123,6 +2321,9 @@
       <c r="M30" s="6"/>
       <c r="N30" s="7"/>
       <c r="O30" s="6"/>
+      <c r="P30" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
@@ -2154,9 +2355,126 @@
       <c r="M31" s="6"/>
       <c r="N31" s="7"/>
       <c r="O31" s="6"/>
+      <c r="P31" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H32" s="3"/>
+      <c r="I32" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="J32" s="4"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="P32" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H33" s="3"/>
+      <c r="I33" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="J33" s="4"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H34" s="3"/>
+      <c r="I34" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J34" s="4"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>209</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O31"/>
+  <autoFilter ref="A1:P34"/>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F31" type="list">
       <formula1>"Disponível,Pendente,A confirmar,A corrigir,Descartado"</formula1>
@@ -2205,7 +2523,7 @@
         <v>142</v>
       </c>
       <c r="B4" s="11" t="n">
-        <f aca="false">COUNTA(Inventário!A2:A31)</f>
+        <f aca="false">COUNTA(Inventário!A2:A34)</f>
         <v>30</v>
       </c>
     </row>
@@ -2214,7 +2532,7 @@
         <v>143</v>
       </c>
       <c r="B5" s="11" t="n">
-        <f aca="false">COUNTIF(Inventário!E2:E31,"Sim")</f>
+        <f aca="false">COUNTIF(Inventário!E2:E34,"Sim")</f>
         <v>28</v>
       </c>
     </row>
@@ -2223,7 +2541,7 @@
         <v>144</v>
       </c>
       <c r="B6" s="11" t="n">
-        <f aca="false">COUNTIF(Inventário!F2:F31,"Disponível")</f>
+        <f aca="false">COUNTIF(Inventário!F2:F34,"Disponível")</f>
         <v>10</v>
       </c>
     </row>
@@ -2232,7 +2550,7 @@
         <v>145</v>
       </c>
       <c r="B7" s="11" t="n">
-        <f aca="false">COUNTIF(Inventário!F2:F31,"Pendente")</f>
+        <f aca="false">COUNTIF(Inventário!F2:F34,"Pendente")</f>
         <v>13</v>
       </c>
     </row>
@@ -2241,7 +2559,7 @@
         <v>77</v>
       </c>
       <c r="B8" s="11" t="n">
-        <f aca="false">COUNTIF(Inventário!F2:F31,"A confirmar")</f>
+        <f aca="false">COUNTIF(Inventário!F2:F34,"A confirmar")</f>
         <v>5</v>
       </c>
     </row>
@@ -2250,7 +2568,7 @@
         <v>53</v>
       </c>
       <c r="B9" s="11" t="n">
-        <f aca="false">COUNTIF(Inventário!F2:F31,"A corrigir")</f>
+        <f aca="false">COUNTIF(Inventário!F2:F34,"A corrigir")</f>
         <v>2</v>
       </c>
     </row>
@@ -2259,7 +2577,7 @@
         <v>146</v>
       </c>
       <c r="B10" s="11" t="n">
-        <f aca="false">COUNTIFS(Inventário!E2:E31,"Sim",Inventário!F2:F31,"&lt;&gt;Disponível")</f>
+        <f aca="false">COUNTIFS(Inventário!E2:E34,"Sim",Inventário!F2:F34,"&lt;&gt;Disponível")</f>
         <v>20</v>
       </c>
     </row>
@@ -2268,7 +2586,7 @@
         <v>147</v>
       </c>
       <c r="B11" s="11" t="n">
-        <f aca="false">COUNTIF(Inventário!L2:L31,"Sim")</f>
+        <f aca="false">COUNTIF(Inventário!L2:L34,"Sim")</f>
         <v>0</v>
       </c>
     </row>
@@ -2277,7 +2595,7 @@
         <v>148</v>
       </c>
       <c r="B12" s="11" t="n">
-        <f aca="false">COUNTIFS(Inventário!E2:E31,"Sim",Inventário!L2:L31,"&lt;&gt;Sim")</f>
+        <f aca="false">COUNTIFS(Inventário!E2:E34,"Sim",Inventário!L2:L34,"&lt;&gt;Sim")</f>
         <v>28</v>
       </c>
     </row>
@@ -2286,7 +2604,7 @@
         <v>149</v>
       </c>
       <c r="B13" s="11" t="n">
-        <f aca="false">SUMPRODUCT((Inventário!G2:G31&lt;&gt;"")*(ISNUMBER(SEARCH("Google",Inventário!G2:G31))+ISNUMBER(SEARCH("Figma",Inventário!G2:G31))&gt;0))</f>
+        <f aca="false">SUMPRODUCT((Inventário!G2:G34&lt;&gt;"")*(ISNUMBER(SEARCH("Google",Inventário!G2:G34))+ISNUMBER(SEARCH("Figma",Inventário!G2:G34))&gt;0))</f>
         <v>13</v>
       </c>
     </row>
@@ -2306,11 +2624,11 @@
         <v>16</v>
       </c>
       <c r="B17" s="14" t="n">
-        <f aca="false">COUNTIF(Inventário!B2:B31,A17)</f>
+        <f aca="false">COUNTIF(Inventário!B2:B34,A17)</f>
         <v>10</v>
       </c>
       <c r="C17" s="14" t="n">
-        <f aca="false">COUNTIFS(Inventário!B2:B31,A17,Inventário!F2:F31,"Disponível")</f>
+        <f aca="false">COUNTIFS(Inventário!B2:B34,A17,Inventário!F2:F34,"Disponível")</f>
         <v>4</v>
       </c>
     </row>
@@ -2319,11 +2637,11 @@
         <v>61</v>
       </c>
       <c r="B18" s="14" t="n">
-        <f aca="false">COUNTIF(Inventário!B2:B31,A18)</f>
+        <f aca="false">COUNTIF(Inventário!B2:B34,A18)</f>
         <v>12</v>
       </c>
       <c r="C18" s="14" t="n">
-        <f aca="false">COUNTIFS(Inventário!B2:B31,A18,Inventário!F2:F31,"Disponível")</f>
+        <f aca="false">COUNTIFS(Inventário!B2:B34,A18,Inventário!F2:F34,"Disponível")</f>
         <v>3</v>
       </c>
     </row>
@@ -2332,11 +2650,11 @@
         <v>105</v>
       </c>
       <c r="B19" s="14" t="n">
-        <f aca="false">COUNTIF(Inventário!B2:B31,A19)</f>
+        <f aca="false">COUNTIF(Inventário!B2:B34,A19)</f>
         <v>4</v>
       </c>
       <c r="C19" s="14" t="n">
-        <f aca="false">COUNTIFS(Inventário!B2:B31,A19,Inventário!F2:F31,"Disponível")</f>
+        <f aca="false">COUNTIFS(Inventário!B2:B34,A19,Inventário!F2:F34,"Disponível")</f>
         <v>1</v>
       </c>
     </row>
@@ -2345,11 +2663,11 @@
         <v>122</v>
       </c>
       <c r="B20" s="14" t="n">
-        <f aca="false">COUNTIF(Inventário!B2:B31,A20)</f>
+        <f aca="false">COUNTIF(Inventário!B2:B34,A20)</f>
         <v>2</v>
       </c>
       <c r="C20" s="14" t="n">
-        <f aca="false">COUNTIFS(Inventário!B2:B31,A20,Inventário!F2:F31,"Disponível")</f>
+        <f aca="false">COUNTIFS(Inventário!B2:B34,A20,Inventário!F2:F34,"Disponível")</f>
         <v>2</v>
       </c>
     </row>
@@ -2358,11 +2676,11 @@
         <v>134</v>
       </c>
       <c r="B21" s="14" t="n">
-        <f aca="false">COUNTIF(Inventário!B2:B31,A21)</f>
+        <f aca="false">COUNTIF(Inventário!B2:B34,A21)</f>
         <v>2</v>
       </c>
       <c r="C21" s="14" t="n">
-        <f aca="false">COUNTIFS(Inventário!B2:B31,A21,Inventário!F2:F31,"Disponível")</f>
+        <f aca="false">COUNTIFS(Inventário!B2:B34,A21,Inventário!F2:F34,"Disponível")</f>
         <v>0</v>
       </c>
     </row>
